--- a/delivery_order_templates/048_inventory_transfer_form--delivery_order_templates.xlsx
+++ b/delivery_order_templates/048_inventory_transfer_form--delivery_order_templates.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -964,8 +964,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
-    <col width="33" customWidth="1" min="2" max="2"/>
-    <col width="33" customWidth="1" min="3" max="3"/>
+    <col width="11" customWidth="1" min="2" max="2"/>
+    <col width="11" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -993,12 +993,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'member1'}</t>
+          <t>member1</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Member1'}</t>
+          <t>Member1</t>
         </is>
       </c>
     </row>
@@ -1010,12 +1010,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'member2'}</t>
+          <t>member2</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Member2'}</t>
+          <t>Member2</t>
         </is>
       </c>
     </row>
@@ -1027,12 +1027,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'member3'}</t>
+          <t>member3</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Member3'}</t>
+          <t>Member3</t>
         </is>
       </c>
     </row>
@@ -1044,12 +1044,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'member1'}</t>
+          <t>member1</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Member1'}</t>
+          <t>Member1</t>
         </is>
       </c>
     </row>
@@ -1061,12 +1061,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'member2'}</t>
+          <t>member2</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Member2'}</t>
+          <t>Member2</t>
         </is>
       </c>
     </row>
@@ -1078,12 +1078,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'member3'}</t>
+          <t>member3</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Member3'}</t>
+          <t>Member3</t>
         </is>
       </c>
     </row>
@@ -1095,12 +1095,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'completed'}</t>
+          <t>completed</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Completed'}</t>
+          <t>Completed</t>
         </is>
       </c>
     </row>
@@ -1112,12 +1112,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'pending'}</t>
+          <t>pending</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Pending'}</t>
+          <t>Pending</t>
         </is>
       </c>
     </row>
@@ -1129,12 +1129,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'cancelled'}</t>
+          <t>cancelled</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Cancelled'}</t>
+          <t>Cancelled</t>
         </is>
       </c>
     </row>
@@ -1146,12 +1146,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'type_1'}</t>
+          <t>type_1</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Type 1'}</t>
+          <t>Type 1</t>
         </is>
       </c>
     </row>
@@ -1163,12 +1163,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'type_2'}</t>
+          <t>type_2</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Type 2'}</t>
+          <t>Type 2</t>
         </is>
       </c>
     </row>
@@ -1180,12 +1180,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'type_3'}</t>
+          <t>type_3</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Type 3'}</t>
+          <t>Type 3</t>
         </is>
       </c>
     </row>
